--- a/results/Int Task Remove ACC 0.5/Rando_9_permute.xlsx
+++ b/results/Int Task Remove ACC 0.5/Rando_9_permute.xlsx
@@ -440,827 +440,827 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.5774631138081862</v>
+        <v>0.5678742520026345</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>scl_entropy</t>
+          <t>bvp_n_sign_changes</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.5964853271485749</v>
+        <v>0.5589517622620904</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>scl_sum</t>
+          <t>hrv_pct_95</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.6087129378915903</v>
+        <v>0.5591255678587713</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>bvp_energy</t>
+          <t>scl_energy</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.6088972984840211</v>
+        <v>0.5485649427778497</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>scr_perm_entropy</t>
+          <t>scl_pct_5</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.6160606222662561</v>
+        <v>0.5552884750705074</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>scl_n_above_mean</t>
+          <t>scr_energy</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.6186494108905038</v>
+        <v>0.5524231455576134</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>scl_perm_entropy</t>
+          <t>bvp_peaks</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.6180252588084958</v>
+        <v>0.5395242370849072</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>bvp_min</t>
+          <t>scl_entropy</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.6261603458661007</v>
+        <v>0.5405065553560271</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr_5_95</t>
+          <t>bvp_pct_95</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.613666749230189</v>
+        <v>0.5535138284517651</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_below_mean</t>
+          <t>scr_lineintegral</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.5799414268102521</v>
+        <v>0.5418998147950079</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>hrv_svd_entropy</t>
+          <t>bvp_max</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.5811897309742683</v>
+        <v>0.5404777050343108</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>hrv_lineintegral</t>
+          <t>scl_lineintegral</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.5915976604500087</v>
+        <v>0.5327718544705332</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>bvp_std</t>
+          <t>bvp_mean</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.5736787959986714</v>
+        <v>0.533130020659645</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>hrv_peaks</t>
+          <t>scr_entropy</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.5736787959986714</v>
+        <v>0.5334881868487568</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>scr_lineintegral</t>
+          <t>hrv_n_below_mean</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.5806683141842255</v>
+        <v>0.533130020659645</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>bvp_ptp</t>
+          <t>scr_pct_95</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.5798914664970362</v>
+        <v>0.5338463530378685</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>hrv_ptp</t>
+          <t>scl_iqr</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.5915160351495432</v>
+        <v>0.5335803671449721</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_95</t>
+          <t>scr_n_above_mean</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.6150206033517037</v>
+        <v>0.5334987418445066</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_above_mean</t>
+          <t>bvp_perm_entropy</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.6025058967242922</v>
+        <v>0.5380022066977781</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>scl_n_below_mean</t>
+          <t>bvp_kurtosis</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.6085025416429766</v>
+        <v>0.5684540731024932</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>scr_energy</t>
+          <t>scl_iqr_5_95</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.5957218491226688</v>
+        <v>0.5804473629398619</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>hrv_min</t>
+          <t>scr_n_below_mean</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.6207512623774917</v>
+        <v>0.5822381938854205</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_95</t>
+          <t>hrv_lineintegral</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.6350040249717126</v>
+        <v>0.5922351821933</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>scr_min</t>
+          <t>scr_std</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.6350040249717126</v>
+        <v>0.5903521709515258</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>scl_std</t>
+          <t>bvp_std</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.6396496304344155</v>
+        <v>0.5763442842587015</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>scr_n_below_mean</t>
+          <t>scl_ptp</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.6360679685432979</v>
+        <v>0.5666132818437185</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr</t>
+          <t>hrv_max</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.6399866866320275</v>
+        <v>0.5617833157885849</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr</t>
+          <t>bvp_rms</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.6067616710106338</v>
+        <v>0.5618754960848003</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>scr_svd_entropy</t>
+          <t>hrv_kurtosis</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.6045204935797479</v>
+        <v>0.5615173298956885</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>bvp_lineintegral</t>
+          <t>hrv_iqr_5_95</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.5945446152633682</v>
+        <v>0.5353423477688146</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>scr_kurtosis</t>
+          <t>scr_n_sign_changes</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.5943602546709374</v>
+        <v>0.5353423477688146</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_above_mean</t>
+          <t>scl_rms</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.5870020153005218</v>
+        <v>0.5469669164213217</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>scr_n_sign_changes</t>
+          <t>scl_std</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.5870020153005218</v>
+        <v>0.5429349080448771</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>bvp_entropy</t>
+          <t>bvp_lineintegral</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.5870020153005218</v>
+        <v>0.5499638315478972</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>hrv_rms</t>
+          <t>scl_pct_95</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.6098402114376749</v>
+        <v>0.5600530001519919</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr_5_95</t>
+          <t>hrv_svd_entropy</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.601407473499924</v>
+        <v>0.5256718606627975</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>hrv_perm_entropy</t>
+          <t>hrv_mean</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.6067799663366003</v>
+        <v>0.5236150438243423</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_sign_changes</t>
+          <t>scl_n_below_mean</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.6067799663366003</v>
+        <v>0.521916393174999</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>scl_max</t>
+          <t>scl_n_sign_changes</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.5836307496580182</v>
+        <v>0.5353106827815651</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr</t>
+          <t>scl_svd_entropy</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.5755378825834127</v>
+        <v>0.5476304738207959</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>scr_sum</t>
+          <t>scl_sum</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.5693252120850479</v>
+        <v>0.5560209917755473</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_5</t>
+          <t>scr_min</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.5754034823041978</v>
+        <v>0.5560209917755473</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>scl_energy</t>
+          <t>scr_perm_entropy</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.5350439932222855</v>
+        <v>0.5466481555496761</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>hrv_kurtosis</t>
+          <t>scl_max</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.5284443062130927</v>
+        <v>0.5553862846977894</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_sign_changes</t>
+          <t>scl_min</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.5209333712374958</v>
+        <v>0.5347576010042727</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>hrv_entropy</t>
+          <t>scl_peaks</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.5109258279338666</v>
+        <v>0.5347576010042727</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>scr_n_above_mean</t>
+          <t>scr_svd_entropy</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.5080710534167224</v>
+        <v>0.5315446602980168</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr</t>
+          <t>scr_mean</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.5017662026221424</v>
+        <v>0.6201060003039839</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>scl_skewness</t>
+          <t>bvp_skewness</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.4982767210272403</v>
+        <v>0.6552745424761175</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>hrv_energy</t>
+          <t>hrv_n_sign_changes</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.4976919742626984</v>
+        <v>0.6552745424761175</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>bvp_rms</t>
+          <t>scr_pct_5</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.5104304468000067</v>
+        <v>0.6806199019370528</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_5</t>
+          <t>scr_peaks</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.4849957217083893</v>
+        <v>0.6806199019370528</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_below_mean</t>
+          <t>bvp_pct_5</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.4919535749066938</v>
+        <v>0.7305021081844845</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>bvp_kurtosis</t>
+          <t>scr_iqr_5_95</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.5261292438119578</v>
+        <v>0.7853064607832652</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>hrv_max</t>
+          <t>scl_n_above_mean</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.5277040491778362</v>
+        <v>0.7927146604668966</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>scr_max</t>
+          <t>hrv_entropy</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.5129664604455052</v>
+        <v>0.7976867671314618</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_5</t>
+          <t>scr_rms</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.5209460372323957</v>
+        <v>0.7775295399147719</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>scl_n_sign_changes</t>
+          <t>scr_skewness</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.5170983894483818</v>
+        <v>0.7764761513389364</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>scl_min</t>
+          <t>scr_max</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.5491123952240755</v>
+        <v>0.6967345657815482</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>hrv_sum</t>
+          <t>hrv_energy</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.5473532292657664</v>
+        <v>0.6508421479275618</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>bvp_svd_entropy</t>
+          <t>hrv_sum</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.5318627175032791</v>
+        <v>0.619510698543692</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr_5_95</t>
+          <t>scl_kurtosis</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.5244967378026469</v>
+        <v>0.6243301096030758</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>scl_kurtosis</t>
+          <t>scr_sum</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.5252130701808704</v>
+        <v>0.6241879689936445</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>scl_svd_entropy</t>
+          <t>hrv_ptp</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.5212521321091415</v>
+        <v>0.578132300538727</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>scr_entropy</t>
+          <t>scr_iqr</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.5202698138380216</v>
+        <v>0.5413073277002494</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>scr_skewness</t>
+          <t>bvp_min</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.5170069128185497</v>
+        <v>0.6015446884446721</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>scr_mean</t>
+          <t>scl_skewness</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.5433057402288886</v>
+        <v>0.6006439954740178</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>hrv_skewness</t>
+          <t>bvp_energy</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.5426815881468805</v>
+        <v>0.6015629837706385</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>scl_mean</t>
+          <t>bvp_ptp</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.5453836670588434</v>
+        <v>0.599250736035037</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>scl_peaks</t>
+          <t>bvp_n_below_mean</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.5453836670588434</v>
+        <v>0.5532583975546186</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr_5_95</t>
+          <t>bvp_n_above_mean</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.5407880219093566</v>
+        <v>0.5228114568145867</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>scr_std</t>
+          <t>scl_perm_entropy</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.5313068210604533</v>
+        <v>0.5195063358121155</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>bvp_peaks</t>
+          <t>bvp_svd_entropy</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.5015691760348118</v>
+        <v>0.5389711553076149</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>scr_ptp</t>
+          <t>scl_mean</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.4822992721274931</v>
+        <v>0.5316734312461651</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>scr_rms</t>
+          <t>hrv_perm_entropy</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.4766157587493878</v>
+        <v>0.5305989326788298</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>scr_peaks</t>
+          <t>hrv_iqr</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.4729524715578048</v>
+        <v>0.5308860285632259</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>bvp_mean</t>
+          <t>hrv_peaks</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.4729524715578048</v>
+        <v>0.526240423100523</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>bvp_skewness</t>
+          <t>scr_kurtosis</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.4497666642272899</v>
+        <v>0.5307938482670104</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>scl_lineintegral</t>
+          <t>hrv_skewness</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.4671007819140852</v>
+        <v>0.5329428454016809</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_5</t>
+          <t>scr_ptp</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.5214758980190384</v>
+        <v>0.5324502789333544</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>scl_rms</t>
+          <t>hrv_rms</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.4915982233831154</v>
+        <v>0.5295743944247105</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>scl_ptp</t>
+          <t>hrv_n_above_mean</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.5039440500785292</v>
+        <v>0.5364717323140491</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>bvp_perm_entropy</t>
+          <t>hrv_std</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.4443153607556814</v>
+        <v>0.5168675868746517</v>
       </c>
     </row>
     <row r="85">
@@ -1270,57 +1270,57 @@
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.4451238734301203</v>
+        <v>0.5168675868746517</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>bvp_max</t>
+          <t>bvp_iqr</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.4663527845486121</v>
+        <v>0.502332654060718</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>hrv_mean</t>
+          <t>bvp_entropy</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.4720067439386177</v>
+        <v>0.502332654060718</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>hrv_std</t>
+          <t>hrv_min</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.4711799359382125</v>
+        <v>0.4988931327790319</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_95</t>
+          <t>bvp_iqr_5_95</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.4677193046650266</v>
+        <v>0.5068304895829229</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_95</t>
+          <t>hrv_pct_5</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.4978179305453133</v>
+        <v>0.5121502074408497</v>
       </c>
     </row>
   </sheetData>
